--- a/CastleHero_Table/Mob_Wave_Table.xlsx
+++ b/CastleHero_Table/Mob_Wave_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AF601C-B77B-4515-B1D0-7EF4FB9567F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2CB471-4C22-4F57-A691-2DAD2FDCF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="1230" windowWidth="30670" windowHeight="19010" xr2:uid="{B044B0ED-9865-4B6E-996D-6C2909E09DF3}"/>
+    <workbookView xWindow="7050" yWindow="1280" windowWidth="30700" windowHeight="19010" xr2:uid="{B044B0ED-9865-4B6E-996D-6C2909E09DF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,87 +36,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Wave_Grp_ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>몬스터 웨이브 그룹 ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Index</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>몬스터 웨이브 등장 순서</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Delay</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>웨이브 시작 시간</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Pattern</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>몬스터 웨이브 등장 패턴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Mob_Delay_1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>몬스터 등장 딜레이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Spawn_1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>몬스터가 생성 되는 위치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Mob_ID_1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>등장하는 몬스터의 ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Mob_Lv_1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>등장하는 몬스터의 레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wave_Grp_Mob_Value_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>등장하는 몬스터의 수량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 순차적 생성
-1 동시 생성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>딜레이 만큼 몬스터 순차적 생성	
-딜레이 후 몬스터 한번에 모두 생성</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -217,18 +171,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -266,7 +214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -276,13 +224,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -619,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF89D3F8-F7F0-44EF-9DB7-8F8BE49C7C56}">
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -651,237 +593,271 @@
     <col min="30" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
+      <c r="X1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>20001</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="2">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="L2" s="2">
+        <v>20002</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2">
+        <v>10</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>20003</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2">
+        <v>10</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>35</v>
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>20001</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>10</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2">
+        <v>20002</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2">
+        <v>10</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="P3" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>20003</v>
+      </c>
+      <c r="R3" s="2">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2">
+        <v>10</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="U3" s="2">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2">
+        <v>20001</v>
+      </c>
+      <c r="W3" s="2">
+        <v>1</v>
+      </c>
+      <c r="X3" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>20002</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" s="2">
         <v>20001</v>
@@ -893,10 +869,10 @@
         <v>10</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L4" s="2">
         <v>20002</v>
@@ -908,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="O4" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="P4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="2">
         <v>20003</v>
@@ -922,35 +898,55 @@
       <c r="S4" s="2">
         <v>10</v>
       </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
+      <c r="T4" s="2">
+        <v>5</v>
+      </c>
+      <c r="U4" s="2">
+        <v>2</v>
+      </c>
+      <c r="V4" s="2">
+        <v>20001</v>
+      </c>
+      <c r="W4" s="2">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>20002</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>0.1</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>20001</v>
@@ -962,7 +958,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="2">
         <v>2</v>
@@ -977,10 +973,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="P5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="2">
         <v>20003</v>
@@ -992,10 +988,10 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="U5" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V5" s="2">
         <v>20001</v>
@@ -1007,10 +1003,10 @@
         <v>10</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="Z5" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="2">
         <v>20002</v>
@@ -1024,111 +1020,81 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
         <v>8</v>
       </c>
       <c r="G6" s="2">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2">
         <v>11</v>
       </c>
       <c r="L6" s="2">
-        <v>20002</v>
+        <v>20003</v>
       </c>
       <c r="M6" s="2">
         <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>10</v>
-      </c>
-      <c r="O6" s="2">
-        <v>5</v>
-      </c>
-      <c r="P6" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>20003</v>
-      </c>
-      <c r="R6" s="2">
-        <v>1</v>
-      </c>
-      <c r="S6" s="2">
-        <v>10</v>
-      </c>
-      <c r="T6" s="2">
-        <v>5</v>
-      </c>
-      <c r="U6" s="2">
-        <v>2</v>
-      </c>
-      <c r="V6" s="2">
-        <v>20001</v>
-      </c>
-      <c r="W6" s="2">
-        <v>1</v>
-      </c>
-      <c r="X6" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>5</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>2</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>20002</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2">
         <v>20001</v>
@@ -1137,13 +1103,13 @@
         <v>1</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2">
         <v>20002</v>
@@ -1155,10 +1121,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="2">
         <v>20003</v>
@@ -1167,57 +1133,37 @@
         <v>1</v>
       </c>
       <c r="S7" s="2">
-        <v>10</v>
-      </c>
-      <c r="T7" s="2">
-        <v>5</v>
-      </c>
-      <c r="U7" s="2">
-        <v>7</v>
-      </c>
-      <c r="V7" s="2">
-        <v>20001</v>
-      </c>
-      <c r="W7" s="2">
-        <v>1</v>
-      </c>
-      <c r="X7" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>5</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>20002</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>10</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2">
         <v>20003</v>
@@ -1226,48 +1172,76 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L8" s="2">
-        <v>20003</v>
+        <v>20001</v>
       </c>
       <c r="M8" s="2">
         <v>1</v>
       </c>
       <c r="N8" s="2">
-        <v>20</v>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>20002</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2">
+        <v>5</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>5</v>
+      </c>
+      <c r="V8" s="2">
+        <v>20001</v>
+      </c>
       <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
+      <c r="X8" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>20001</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>3</v>
       </c>
       <c r="B9" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -1276,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
         <v>20001</v>
@@ -1288,10 +1262,10 @@
         <v>5</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2">
         <v>20002</v>
@@ -1300,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O9" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="2">
         <v>20003</v>
@@ -1333,10 +1307,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -1345,195 +1319,39 @@
         <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2">
-        <v>20003</v>
+        <v>30021</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="K10" s="2">
-        <v>10</v>
-      </c>
-      <c r="L10" s="2">
-        <v>20001</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2">
-        <v>10</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>20002</v>
-      </c>
-      <c r="R10" s="2">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2">
-        <v>5</v>
-      </c>
-      <c r="T10" s="2">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2">
-        <v>5</v>
-      </c>
-      <c r="V10" s="2">
-        <v>20001</v>
-      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>20001</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A11" s="2">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2">
-        <v>20001</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
-        <v>5</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
-      <c r="L11" s="2">
-        <v>20002</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2">
-        <v>5</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>20003</v>
-      </c>
-      <c r="R11" s="2">
-        <v>1</v>
-      </c>
-      <c r="S11" s="2">
-        <v>5</v>
-      </c>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A12" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>30</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2">
-        <v>30021</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/CastleHero_Table/Mob_Wave_Table.xlsx
+++ b/CastleHero_Table/Mob_Wave_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\작업폴더\01. 캐슬히어로\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2CB471-4C22-4F57-A691-2DAD2FDCF285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1DA1A0-214D-483C-ACF9-56E91CD7D587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="1280" windowWidth="30700" windowHeight="19010" xr2:uid="{B044B0ED-9865-4B6E-996D-6C2909E09DF3}"/>
+    <workbookView xWindow="39540" yWindow="1140" windowWidth="30700" windowHeight="19010" xr2:uid="{B044B0ED-9865-4B6E-996D-6C2909E09DF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Wave_Grp_ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -131,6 +131,10 @@
   </si>
   <si>
     <t>Wave_Grp_Mob_Delay_5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Grp_Mob_Delay_3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,6 +185,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -214,7 +224,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -225,6 +235,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -561,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF89D3F8-F7F0-44EF-9DB7-8F8BE49C7C56}">
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -637,7 +650,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>13</v>
@@ -696,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
@@ -707,11 +720,11 @@
       <c r="H2" s="2">
         <v>1</v>
       </c>
-      <c r="I2" s="2">
-        <v>10</v>
+      <c r="I2" s="4">
+        <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2">
         <v>3</v>
@@ -722,11 +735,11 @@
       <c r="M2" s="2">
         <v>1</v>
       </c>
-      <c r="N2" s="2">
-        <v>10</v>
+      <c r="N2" s="4">
+        <v>3</v>
       </c>
       <c r="O2" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="P2" s="2">
         <v>1</v>
@@ -737,19 +750,19 @@
       <c r="R2" s="2">
         <v>1</v>
       </c>
-      <c r="S2" s="2">
-        <v>10</v>
+      <c r="S2" s="4">
+        <v>3</v>
       </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
+      <c r="X2" s="4"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
+      <c r="AC2" s="4"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
@@ -765,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -776,11 +789,11 @@
       <c r="H3" s="2">
         <v>1</v>
       </c>
-      <c r="I3" s="2">
-        <v>10</v>
+      <c r="I3" s="4">
+        <v>3</v>
       </c>
       <c r="J3" s="2">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2">
         <v>2</v>
@@ -791,11 +804,11 @@
       <c r="M3" s="2">
         <v>1</v>
       </c>
-      <c r="N3" s="2">
-        <v>10</v>
+      <c r="N3" s="4">
+        <v>3</v>
       </c>
       <c r="O3" s="2">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="2">
         <v>1</v>
@@ -806,11 +819,11 @@
       <c r="R3" s="2">
         <v>1</v>
       </c>
-      <c r="S3" s="2">
-        <v>10</v>
+      <c r="S3" s="4">
+        <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="U3" s="2">
         <v>3</v>
@@ -821,11 +834,11 @@
       <c r="W3" s="2">
         <v>1</v>
       </c>
-      <c r="X3" s="2">
-        <v>10</v>
+      <c r="X3" s="4">
+        <v>3</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="Z3" s="2">
         <v>2</v>
@@ -836,8 +849,8 @@
       <c r="AB3" s="2">
         <v>1</v>
       </c>
-      <c r="AC3" s="2">
-        <v>10</v>
+      <c r="AC3" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
@@ -865,8 +878,8 @@
       <c r="H4" s="2">
         <v>1</v>
       </c>
-      <c r="I4" s="2">
-        <v>10</v>
+      <c r="I4" s="4">
+        <v>3</v>
       </c>
       <c r="J4" s="2">
         <v>5</v>
@@ -880,8 +893,8 @@
       <c r="M4" s="2">
         <v>1</v>
       </c>
-      <c r="N4" s="2">
-        <v>10</v>
+      <c r="N4" s="4">
+        <v>3</v>
       </c>
       <c r="O4" s="2">
         <v>5</v>
@@ -895,8 +908,8 @@
       <c r="R4" s="2">
         <v>1</v>
       </c>
-      <c r="S4" s="2">
-        <v>10</v>
+      <c r="S4" s="4">
+        <v>3</v>
       </c>
       <c r="T4" s="2">
         <v>5</v>
@@ -910,8 +923,8 @@
       <c r="W4" s="2">
         <v>1</v>
       </c>
-      <c r="X4" s="2">
-        <v>10</v>
+      <c r="X4" s="4">
+        <v>3</v>
       </c>
       <c r="Y4" s="2">
         <v>5</v>
@@ -925,8 +938,8 @@
       <c r="AB4" s="2">
         <v>1</v>
       </c>
-      <c r="AC4" s="2">
-        <v>10</v>
+      <c r="AC4" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
@@ -954,8 +967,8 @@
       <c r="H5" s="2">
         <v>1</v>
       </c>
-      <c r="I5" s="2">
-        <v>10</v>
+      <c r="I5" s="4">
+        <v>3</v>
       </c>
       <c r="J5" s="2">
         <v>5</v>
@@ -969,8 +982,8 @@
       <c r="M5" s="2">
         <v>1</v>
       </c>
-      <c r="N5" s="2">
-        <v>10</v>
+      <c r="N5" s="4">
+        <v>3</v>
       </c>
       <c r="O5" s="2">
         <v>5</v>
@@ -984,8 +997,8 @@
       <c r="R5" s="2">
         <v>1</v>
       </c>
-      <c r="S5" s="2">
-        <v>10</v>
+      <c r="S5" s="4">
+        <v>5</v>
       </c>
       <c r="T5" s="2">
         <v>5</v>
@@ -999,8 +1012,8 @@
       <c r="W5" s="2">
         <v>1</v>
       </c>
-      <c r="X5" s="2">
-        <v>10</v>
+      <c r="X5" s="4">
+        <v>5</v>
       </c>
       <c r="Y5" s="2">
         <v>5</v>
@@ -1014,8 +1027,8 @@
       <c r="AB5" s="2">
         <v>1</v>
       </c>
-      <c r="AC5" s="2">
-        <v>10</v>
+      <c r="AC5" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
@@ -1043,8 +1056,8 @@
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="2">
-        <v>20</v>
+      <c r="I6" s="4">
+        <v>5</v>
       </c>
       <c r="J6" s="2">
         <v>1</v>
@@ -1058,24 +1071,24 @@
       <c r="M6" s="2">
         <v>1</v>
       </c>
-      <c r="N6" s="2">
-        <v>20</v>
+      <c r="N6" s="4">
+        <v>5</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="S6" s="4"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
+      <c r="X6" s="4"/>
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
+      <c r="AC6" s="4"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
@@ -1102,8 +1115,8 @@
       <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="I7" s="2">
-        <v>5</v>
+      <c r="I7" s="4">
+        <v>3</v>
       </c>
       <c r="J7" s="2">
         <v>3</v>
@@ -1117,8 +1130,8 @@
       <c r="M7" s="2">
         <v>1</v>
       </c>
-      <c r="N7" s="2">
-        <v>10</v>
+      <c r="N7" s="4">
+        <v>3</v>
       </c>
       <c r="O7" s="2">
         <v>3</v>
@@ -1132,19 +1145,19 @@
       <c r="R7" s="2">
         <v>1</v>
       </c>
-      <c r="S7" s="2">
-        <v>5</v>
+      <c r="S7" s="4">
+        <v>3</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
+      <c r="X7" s="4"/>
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
+      <c r="AC7" s="4"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
@@ -1171,7 +1184,7 @@
       <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="4">
         <v>5</v>
       </c>
       <c r="J8" s="2">
@@ -1186,8 +1199,8 @@
       <c r="M8" s="2">
         <v>1</v>
       </c>
-      <c r="N8" s="2">
-        <v>10</v>
+      <c r="N8" s="4">
+        <v>3</v>
       </c>
       <c r="O8" s="2">
         <v>0</v>
@@ -1201,8 +1214,8 @@
       <c r="R8" s="2">
         <v>1</v>
       </c>
-      <c r="S8" s="2">
-        <v>5</v>
+      <c r="S8" s="4">
+        <v>3</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
@@ -1214,8 +1227,8 @@
         <v>20001</v>
       </c>
       <c r="W8" s="2"/>
-      <c r="X8" s="2">
-        <v>5</v>
+      <c r="X8" s="4">
+        <v>3</v>
       </c>
       <c r="Y8" s="2">
         <v>0</v>
@@ -1229,8 +1242,8 @@
       <c r="AB8" s="2">
         <v>1</v>
       </c>
-      <c r="AC8" s="2">
-        <v>5</v>
+      <c r="AC8" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
@@ -1258,8 +1271,8 @@
       <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="I9" s="2">
-        <v>5</v>
+      <c r="I9" s="4">
+        <v>3</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
@@ -1273,7 +1286,7 @@
       <c r="M9" s="2">
         <v>1</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="4">
         <v>5</v>
       </c>
       <c r="O9" s="2">
@@ -1288,19 +1301,19 @@
       <c r="R9" s="2">
         <v>1</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9" s="4">
         <v>5</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
+      <c r="X9" s="4"/>
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
+      <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
@@ -1327,7 +1340,7 @@
       <c r="H10" s="2">
         <v>1</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="J10" s="2">
@@ -1336,22 +1349,28 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="4"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+      <c r="S10" s="4"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
+      <c r="X10" s="4"/>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
+      <c r="AC10" s="4"/>
+    </row>
+    <row r="18" spans="24:24" x14ac:dyDescent="0.45">
+      <c r="X18" s="1">
+        <f>+AB18</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
